--- a/document/タスク削除画面_詳細設計書.xlsx
+++ b/document/タスク削除画面_詳細設計書.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B359B9CD-F9C3-40C5-8319-E4A5846AE1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159B2CBD-D61F-4985-BA7D-A90CE2655B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
-    <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="タスク削除完了画面" sheetId="7" r:id="rId5"/>
-    <sheet name="タスク削除確認画面" sheetId="8" r:id="rId6"/>
+    <sheet name="詳細クラス図" sheetId="9" r:id="rId4"/>
+    <sheet name="タスク削除確認画面" sheetId="8" r:id="rId5"/>
+    <sheet name="タスク削除完了画面" sheetId="7" r:id="rId6"/>
     <sheet name="タスク削除失敗画面" sheetId="5" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="104">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -525,6 +525,31 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>削除するタスクの内容が表示されている表</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移するボタン</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移するボタン</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -533,7 +558,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -605,6 +630,18 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1284,10 +1321,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1328,9 +1366,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,20 +1437,134 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1427,82 +1576,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1510,11 +1593,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1525,82 +1611,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1609,21 +1629,139 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{7C4C7BAB-6426-4DE9-A903-E1994185666A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1643,22 +1781,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>105019</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>167566</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>515216</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>41380</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D8A94C2-5E05-A7E1-B5A0-D28804569BB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6349B01B-D09A-4B29-A180-D8A8A268C03E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1667,21 +1805,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="466725" y="1581150"/>
-          <a:ext cx="3743325" cy="3444166"/>
+          <a:off x="590550" y="1181344"/>
+          <a:ext cx="6525491" cy="3822561"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2193,6 +2330,357 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>129466</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D8A94C2-5E05-A7E1-B5A0-D28804569BB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="428625" y="1543050"/>
+          <a:ext cx="3743325" cy="3444166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 線 (枠なし) 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D6BCEEB-99FC-44FD-AAB9-6D8DD5452E67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3943350" y="1905000"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 22199"/>
+            <a:gd name="adj2" fmla="val 5411"/>
+            <a:gd name="adj3" fmla="val 67672"/>
+            <a:gd name="adj4" fmla="val -12267"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="楕円 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E763926-DB2B-4152-9A99-4BD2B384BE43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="333375" y="4543425"/>
+          <a:ext cx="1552575" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>971550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="吹き出し: 線 (枠なし) 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47BDD5A7-56C7-4C17-94D5-DF0D9C771E02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2219325" y="4505325"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 14153"/>
+            <a:gd name="adj2" fmla="val 5411"/>
+            <a:gd name="adj3" fmla="val 28592"/>
+            <a:gd name="adj4" fmla="val -24589"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>695326</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CB8CFD-D570-4E02-A5D3-095BE7F62103}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="447676" y="2486026"/>
+          <a:ext cx="3505200" cy="1981199"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2898,85 +3386,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2996,46 +3484,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="38" t="s">
+      <c r="H13" s="70"/>
+      <c r="I13" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="70"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3044,13 +3532,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4064,19 +4552,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4088,192 +4576,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="67"/>
+      <c r="F2" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="67"/>
+      <c r="H2" s="69">
         <v>46183</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="63" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="63" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="64"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="42"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="63" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="64"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="83" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="64"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="42"/>
     </row>
     <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="83" t="s">
+      <c r="C10" s="70"/>
+      <c r="D10" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="64"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
     </row>
     <row r="11" spans="1:10" ht="111" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="61" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="83" t="s">
+      <c r="C11" s="70"/>
+      <c r="D11" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="64"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="63" t="s">
+      <c r="B12" s="41"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="64"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5264,6 +5752,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5272,25 +5779,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5309,19 +5797,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5333,40 +5821,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6712,422 +7200,431 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1805989-A9D8-4086-A6FF-ADE95A58FF45}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="3" width="5.140625" style="119" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="119" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="119" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="119"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="115"/>
+      <c r="H1" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="118" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="124"/>
+      <c r="F2" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="124"/>
+      <c r="H2" s="125">
+        <v>46183</v>
+      </c>
+      <c r="I2" s="126" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="130"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="136"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="139"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="A6" s="137"/>
+      <c r="B6" s="138"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="139"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
+      <c r="A7" s="137"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="139"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
+      <c r="A9" s="137"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="139"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="A10" s="137"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="139"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="139"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
+      <c r="A12" s="137"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="139"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
+      <c r="A13" s="137"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="139"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
+      <c r="A14" s="137"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="139"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="A15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="139"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
+      <c r="A16" s="137"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
+      <c r="A17" s="137"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="139"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
+      <c r="A18" s="137"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="139"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
+      <c r="A19" s="137"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="139"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="139"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
+      <c r="A21" s="137"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="139"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
+      <c r="A22" s="137"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="139"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
+      <c r="A23" s="137"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="139"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
+      <c r="A24" s="137"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="139"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
+      <c r="A25" s="137"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="139"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
+      <c r="A26" s="137"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="139"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
+      <c r="A27" s="137"/>
+      <c r="B27" s="138"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="139"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
+      <c r="A28" s="137"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="139"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
+      <c r="A29" s="137"/>
+      <c r="B29" s="138"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="139"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="137"/>
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="139"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="139"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="13"/>
+      <c r="A32" s="137"/>
+      <c r="B32" s="138"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="139"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A33" s="140"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="141"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="141"/>
+      <c r="H33" s="141"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="142"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7140,7 +7637,7 @@
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="J44" s="14"/>
+      <c r="J44" s="143"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8100,7 +8597,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
@@ -8108,14 +8604,1491 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B96DB6-1627-474E-89C1-F3D3A6C8D4F9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J1007"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="49"/>
+      <c r="F1" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="49"/>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="67"/>
+      <c r="F2" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="67"/>
+      <c r="H2" s="69">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="45"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="46"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="46"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="51"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="58"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1">
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="58"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="42"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="41"/>
+      <c r="J25" s="42"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="72"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="72"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="72"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="42"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A30" s="73"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="77"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
+    <row r="1002" ht="12.75" customHeight="1"/>
+    <row r="1003" ht="12.75" customHeight="1"/>
+    <row r="1004" ht="12.75" customHeight="1"/>
+    <row r="1005" ht="12.75" customHeight="1"/>
+    <row r="1006" ht="12.75" customHeight="1"/>
+    <row r="1007" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J20"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:C22"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDFE56BA-C113-4CB5-AE0A-851056E3A645}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8129,19 +10102,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8153,384 +10126,400 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="67"/>
+      <c r="F2" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="67"/>
+      <c r="H2" s="69">
         <v>46188</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="97"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="97"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="97"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="97"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="97"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="97"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="71"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="97"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="63" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
+      <c r="B22" s="41"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="17" t="s">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
+      <c r="E23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
+      <c r="E24" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="80"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="77"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9511,6 +11500,21 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="I2:I4"/>
@@ -9527,1496 +11531,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B96DB6-1627-474E-89C1-F3D3A6C8D4F9}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J1007"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="58"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="97"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="97"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="97"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="97"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="97"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="97"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="97"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="71"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="97"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="64"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="85"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="64"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="80"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" ht="12.75" customHeight="1"/>
-    <row r="34" ht="12.75" customHeight="1"/>
-    <row r="35" ht="12.75" customHeight="1"/>
-    <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1"/>
-    <row r="38" ht="12.75" customHeight="1"/>
-    <row r="39" ht="12.75" customHeight="1"/>
-    <row r="40" ht="12.75" customHeight="1"/>
-    <row r="41" ht="12.75" customHeight="1"/>
-    <row r="42" ht="12.75" customHeight="1"/>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12.75" customHeight="1"/>
-    <row r="46" ht="12.75" customHeight="1"/>
-    <row r="47" ht="12.75" customHeight="1"/>
-    <row r="48" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
-    <row r="1002" ht="12.75" customHeight="1"/>
-    <row r="1003" ht="12.75" customHeight="1"/>
-    <row r="1004" ht="12.75" customHeight="1"/>
-    <row r="1005" ht="12.75" customHeight="1"/>
-    <row r="1006" ht="12.75" customHeight="1"/>
-    <row r="1007" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J20"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11039,19 +11553,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11063,388 +11577,412 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="67"/>
+      <c r="F2" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="67"/>
+      <c r="H2" s="69">
         <v>46188</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="97"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="97"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="97"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="97"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="97"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="97"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="71"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="97"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="63" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
+      <c r="B22" s="41"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="17" t="s">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
+      <c r="E23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
+      <c r="E24" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
+    </row>
+    <row r="25" spans="1:10" ht="38.25" customHeight="1">
+      <c r="A25" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="17" t="s">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
+      <c r="E25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="84" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="109"/>
+      <c r="J25" s="110"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="80"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="77"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12425,16 +12963,11 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12451,11 +12984,16 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H29:J29"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12475,182 +13013,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="49"/>
+      <c r="Q1" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="49"/>
+      <c r="S1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="82"/>
+      <c r="T1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="96"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="55"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="97"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="58"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="107"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="81" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="82"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="51"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="63" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="64"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="42"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="63" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="64"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="42"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12675,156 +13213,156 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="23"/>
+      <c r="E9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
       <c r="A14" s="8"/>
@@ -12849,522 +13387,522 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="107" t="s">
+      <c r="B15" s="70"/>
+      <c r="C15" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="91" t="s">
+      <c r="D15" s="70"/>
+      <c r="E15" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="91" t="s">
+      <c r="F15" s="70"/>
+      <c r="G15" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="91" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="91" t="s">
+      <c r="K15" s="70"/>
+      <c r="L15" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="91" t="s">
+      <c r="M15" s="41"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="15" t="s">
+      <c r="P15" s="41"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="S15" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="T15" s="31" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="105">
+      <c r="A16" s="99">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="106" t="s">
+      <c r="B16" s="70"/>
+      <c r="C16" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="106" t="s">
+      <c r="D16" s="70"/>
+      <c r="E16" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="100" t="s">
+      <c r="F16" s="70"/>
+      <c r="G16" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="100" t="s">
+      <c r="H16" s="41"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="70"/>
+      <c r="L16" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="41"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="105">
+      <c r="A17" s="99">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="70"/>
+      <c r="C17" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="106" t="s">
+      <c r="D17" s="70"/>
+      <c r="E17" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="100" t="s">
+      <c r="F17" s="70"/>
+      <c r="G17" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="100" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="70"/>
+      <c r="L17" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="34"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="105"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="34"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="105"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="103"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="34"/>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="105"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="105"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="103"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="105"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="103"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="105"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="103"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="105"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="A24" s="99"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="105"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="A25" s="99"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="103"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="105"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="103"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="105"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="105"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="103"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="105"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="103"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="105"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="103"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="67"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="108"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="34"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31" s="34"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="3"/>
@@ -14353,6 +14891,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14377,118 +15027,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除画面_詳細設計書.xlsx
+++ b/document/タスク削除画面_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B359B9CD-F9C3-40C5-8319-E4A5846AE1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6C868-9F0D-4D39-ACB2-550817727471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="103">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -451,10 +451,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>エラーメッセージ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>削除</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -525,6 +521,28 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>削除したタスクの内容が表示されている表</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移するボタン</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移するボタン</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除ができなかったタスクの内容が表示されている表</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -551,6 +569,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1287,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1618,9 +1637,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1643,15 +1659,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>167566</xdr:rowOff>
+      <xdr:rowOff>148516</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1680,7 +1696,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="466725" y="1581150"/>
+          <a:off x="476250" y="1562100"/>
           <a:ext cx="3743325" cy="3444166"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1688,6 +1704,302 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>971550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="吹き出し: 線 (枠なし) 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74FBA6ED-C1D0-4CDA-9383-283B7414F59F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4229100" y="1952625"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 22199"/>
+            <a:gd name="adj2" fmla="val 5411"/>
+            <a:gd name="adj3" fmla="val 67672"/>
+            <a:gd name="adj4" fmla="val -12267"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="楕円 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2D310AE-6D1D-4302-A078-976719E40C60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="361950" y="4591050"/>
+          <a:ext cx="1552575" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 線 (枠なし) 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECA8D36B-E823-4349-9CCB-73041ADF307B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3990975"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 19900"/>
+            <a:gd name="adj2" fmla="val 11098"/>
+            <a:gd name="adj3" fmla="val 83764"/>
+            <a:gd name="adj4" fmla="val 28492"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B5C039-FA63-414F-8BF0-F06FCD268122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="409576" y="2505075"/>
+          <a:ext cx="3648074" cy="1971675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2196,23 +2508,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>295274</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:rowOff>19872</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>132589</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302AA3AC-8CDB-3AD0-3788-80E1EED4D995}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1BC69F2-883E-B64F-E640-D3D2BAF02075}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2234,8 +2546,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638174" y="1562099"/>
-          <a:ext cx="3866390" cy="3371851"/>
+          <a:off x="190501" y="1562922"/>
+          <a:ext cx="3771899" cy="3332928"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2247,15 +2559,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1085851</xdr:colOff>
+      <xdr:colOff>828676</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>238126</xdr:rowOff>
+      <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>590551</xdr:colOff>
+      <xdr:colOff>333376</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2270,7 +2582,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4343401" y="2047876"/>
+          <a:off x="4086226" y="2066926"/>
           <a:ext cx="1733550" cy="704850"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -2328,16 +2640,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2352,7 +2664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="4505325"/>
+          <a:off x="180975" y="4391025"/>
           <a:ext cx="1552575" cy="381000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -2394,82 +2706,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="楕円 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D7C6687-BA2B-4C76-9202-106029AAB8F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="790576" y="2190750"/>
-          <a:ext cx="2428874" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2484,7 +2730,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2705100" y="4552950"/>
+          <a:off x="2162175" y="4410075"/>
           <a:ext cx="2009775" cy="1362075"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -2542,98 +2788,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="吹き出し: 線 (枠なし) 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C662BBFC-F397-4483-830C-560C178F5EC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3514725" y="2152649"/>
-          <a:ext cx="1419225" cy="200025"/>
-        </a:xfrm>
-        <a:prstGeom prst="callout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 62757"/>
-            <a:gd name="adj2" fmla="val 7504"/>
-            <a:gd name="adj3" fmla="val 112500"/>
-            <a:gd name="adj4" fmla="val -29608"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t>③</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
+      <xdr:colOff>771525</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>219076</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2648,8 +2812,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="790575" y="2524126"/>
-          <a:ext cx="3409950" cy="1905000"/>
+          <a:off x="200024" y="2343151"/>
+          <a:ext cx="3829051" cy="2028824"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8449,10 +8613,18 @@
       <c r="D23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
+      <c r="E23" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>99</v>
+      </c>
       <c r="I23" s="39"/>
       <c r="J23" s="64"/>
     </row>
@@ -8465,10 +8637,18 @@
       <c r="D24" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
+      <c r="E24" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>100</v>
+      </c>
       <c r="I24" s="39"/>
       <c r="J24" s="64"/>
     </row>
@@ -9511,13 +9691,8 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -9525,23 +9700,28 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9897,16 +10077,16 @@
         <v>88</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="63" t="s">
         <v>96</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>97</v>
       </c>
       <c r="I24" s="39"/>
       <c r="J24" s="64"/>
@@ -9918,19 +10098,19 @@
       <c r="B25" s="88"/>
       <c r="C25" s="89"/>
       <c r="D25" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="G25" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="64"/>
@@ -9942,19 +10122,19 @@
       <c r="B26" s="88"/>
       <c r="C26" s="89"/>
       <c r="D26" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="G26" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="64"/>
@@ -10986,13 +11166,8 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11000,23 +11175,28 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11030,7 +11210,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1006"/>
+  <dimension ref="A1:J1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -11150,50 +11330,50 @@
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="98"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
       <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="98"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
       <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
       <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
       <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
@@ -11359,10 +11539,18 @@
       <c r="D23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
+      <c r="E23" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>102</v>
+      </c>
       <c r="I23" s="39"/>
       <c r="J23" s="64"/>
     </row>
@@ -11375,22 +11563,26 @@
       <c r="D24" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
+      <c r="E24" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>101</v>
+      </c>
       <c r="I24" s="39"/>
       <c r="J24" s="64"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="17" t="s">
-        <v>91</v>
-      </c>
+      <c r="A25" s="85"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
@@ -11423,29 +11615,18 @@
       <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="80"/>
-    </row>
+      <c r="A28" s="86"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="80"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12422,23 +12603,20 @@
     <row r="1003" ht="12.75" customHeight="1"/>
     <row r="1004" ht="12.75" customHeight="1"/>
     <row r="1005" ht="12.75" customHeight="1"/>
-    <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="29">
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="D5:J5"/>
@@ -12450,7 +12628,7 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H28:J28"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>

--- a/document/タスク削除画面_詳細設計書.xlsx
+++ b/document/タスク削除画面_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B359B9CD-F9C3-40C5-8319-E4A5846AE1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3A6C86-1ED0-4650-AF24-4B109C29BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="13260" windowHeight="9165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -300,73 +300,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>従業員</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログインが成功している状態であること。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>選択したタスクが削除されタスク削除完了画面が表示される</t>
-    <rPh sb="0" eb="2">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>カンリョウガメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.利用者がタスク一覧画面を表示する
-2.利用者が削除対象のタスクをラジオボタンで選択する
-3.利用者が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する
-5.システムがタスク削除確認画面を表示する
-6.利用者が「削除」ボタンを押下する
-7.システムが選択されたタスクを削除する
-8.システムがタスク削除完了画面を表示する</t>
-    <rPh sb="160" eb="166">
-      <t>サクジョカンリョウガメン</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1:タスク未選択で削除ボタン押下
-A1-1:基本フロー3でタスク未選択を検出
-A1-2:.タスク一覧表示画面で「タスクが存在しません」と表示される</t>
-    <rPh sb="33" eb="36">
-      <t>ミセンタク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ケンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1:削除処理失敗
-E1-1:基本フロー7でシステムがタスク削除処理に失敗する
-E1-2:「システムエラーが発生しました。」を表示する
-E2:データベース接続失敗
-E2-1:基本フロー2「システムエラーが発生しました。」を表示する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>清山</t>
     <rPh sb="0" eb="2">
       <t>セイヤマ</t>
@@ -525,6 +458,99 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>従業員(削除したいタスクの担当者本人)</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホンニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1:削除処理失敗
+E1-1:基本フロー7でシステムがタスク削除処理に失敗する
+E1-2:「システムエラーが発生しました。」を表示する
+E2:データベース接続失敗した場合
+E2-1:システムは削除失敗画面を表示する。
+E2-2:システムは「次のタスクを削除できませんでした」というエラーメッセージを表示する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクがデータベースで削除されタスク削除完了画面が表示される</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1:タスク未選択で削除ボタン押下
+A1-1:基本フロー3でタスク未選択を検出
+A1-2:.タスク一覧表示画面で「タスクが存在しません」と表示される
+A1-3:従業員は基本フロー１に戻る</t>
+    <rPh sb="33" eb="36">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="80" eb="83">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員がタスク一覧画面を表示する
+2.従業員が削除対象のタスクをラジオボタンで選択する
+3.従業員が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得する
+5.システムがタスク削除確認画面を表示する
+6.従業員が「削除」ボタンを押下する
+7.システムが選択されたタスクを削除する
+8.システムがタスク削除完了画面を表示する</t>
+    <rPh sb="2" eb="5">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="160" eb="166">
+      <t>サクジョカンリョウガメン</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -551,6 +577,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1287,7 +1314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1402,20 +1429,134 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1427,82 +1568,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1510,11 +1585,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1525,82 +1603,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1609,17 +1621,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2898,85 +2922,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2996,46 +3020,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="38" t="s">
+      <c r="H13" s="71"/>
+      <c r="I13" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="71"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="71"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3044,13 +3068,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4064,19 +4088,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4088,192 +4112,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46183</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="63" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="64"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="64"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
     </row>
     <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="83" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="64"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
     </row>
     <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="64"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
     </row>
     <row r="11" spans="1:10" ht="111" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="61" t="s">
+      <c r="A11" s="95"/>
+      <c r="B11" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="64"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="43"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="64"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5264,6 +5288,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5272,25 +5315,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5309,19 +5333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5333,40 +5357,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6722,19 +6746,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6746,40 +6770,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8129,19 +8153,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8153,275 +8177,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="58"/>
+      <c r="I2" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="97"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="97"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="97"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="97"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="97"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="97"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="71"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="97"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="59"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
+      <c r="A18" s="60"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="59"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="71"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="71"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8434,103 +8458,103 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
+      <c r="A23" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="A24" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E24" s="17"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="73"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="73"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="43"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="76"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="80"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9511,6 +9535,21 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="I2:I4"/>
@@ -9527,21 +9566,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9564,19 +9588,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9588,287 +9612,287 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="58"/>
+      <c r="I2" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="97"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="97"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="97"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="97"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="97"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="97"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="97"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="59"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
+      <c r="A18" s="60"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="59"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="71"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="97"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="64"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="71"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="71"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -9881,131 +9905,131 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="91" t="s">
+      <c r="H23" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="A24" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="F24" s="17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
+        <v>90</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="A25" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
+      <c r="A26" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="73"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="43"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="85"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="71"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="64"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="43"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="67"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="76"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="80"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="78"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10986,6 +11010,21 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="I2:I4"/>
@@ -11002,21 +11041,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11039,19 +11063,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11063,275 +11087,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="58"/>
+      <c r="I2" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="93" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="97"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="97"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="97"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="97"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="97"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="97"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="71"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="97"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="97"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="97"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="97"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="59"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="97"/>
+      <c r="A18" s="60"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="59"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="97"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="71"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="71"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11344,107 +11368,107 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
+      <c r="A23" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="64"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="A24" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E24" s="17"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="64"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="A25" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="64"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="73"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="64"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="73"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="64"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="43"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="64"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="76"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="80"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12425,16 +12449,11 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12451,11 +12470,16 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H29:J29"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12475,182 +12499,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="50"/>
+      <c r="Q1" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="50"/>
+      <c r="S1" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="82"/>
+      <c r="T1" s="52"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="96"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="97"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="59"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="108"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="81" t="s">
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="82"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="52"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="63" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="64"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="43"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="63" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="64"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="43"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12849,37 +12873,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="71"/>
       <c r="C15" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="91" t="s">
+      <c r="D15" s="71"/>
+      <c r="E15" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="91" t="s">
+      <c r="F15" s="71"/>
+      <c r="G15" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="91" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="91" t="s">
+      <c r="K15" s="71"/>
+      <c r="L15" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="91" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="71"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -12891,37 +12915,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="105">
+      <c r="A16" s="100">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="106" t="s">
+      <c r="B16" s="71"/>
+      <c r="C16" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="106" t="s">
+      <c r="D16" s="71"/>
+      <c r="E16" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="100" t="s">
+      <c r="F16" s="71"/>
+      <c r="G16" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="100" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="71"/>
+      <c r="L16" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="71"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12933,37 +12957,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="105">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="106" t="s">
+      <c r="D17" s="71"/>
+      <c r="E17" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="100" t="s">
+      <c r="F17" s="71"/>
+      <c r="G17" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="100" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="71"/>
+      <c r="L17" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="71"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12975,23 +12999,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="105"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="71"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13003,23 +13027,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="105"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="71"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13031,23 +13055,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="105"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="71"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13059,23 +13083,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="105"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="71"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13087,23 +13111,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="105"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="71"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13115,23 +13139,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="105"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="71"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13143,23 +13167,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="105"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="71"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13171,23 +13195,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="105"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="71"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13199,23 +13223,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="105"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="71"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13227,23 +13251,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="105"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="71"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13255,23 +13279,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="105"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="71"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13283,23 +13307,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="105"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="71"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13311,23 +13335,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="71"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13339,23 +13363,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="67"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="76"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14353,6 +14377,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14377,118 +14513,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除画面_詳細設計書.xlsx
+++ b/document/タスク削除画面_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3A6C86-1ED0-4650-AF24-4B109C29BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6C868-9F0D-4D39-ACB2-550817727471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="13260" windowHeight="9165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="103">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -300,6 +300,73 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>従業員</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインが成功している状態であること。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクが削除されタスク削除完了画面が表示される</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.利用者がタスク一覧画面を表示する
+2.利用者が削除対象のタスクをラジオボタンで選択する
+3.利用者が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得する
+5.システムがタスク削除確認画面を表示する
+6.利用者が「削除」ボタンを押下する
+7.システムが選択されたタスクを削除する
+8.システムがタスク削除完了画面を表示する</t>
+    <rPh sb="160" eb="166">
+      <t>サクジョカンリョウガメン</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1:タスク未選択で削除ボタン押下
+A1-1:基本フロー3でタスク未選択を検出
+A1-2:.タスク一覧表示画面で「タスクが存在しません」と表示される</t>
+    <rPh sb="33" eb="36">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1:削除処理失敗
+E1-1:基本フロー7でシステムがタスク削除処理に失敗する
+E1-2:「システムエラーが発生しました。」を表示する
+E2:データベース接続失敗
+E2-1:基本フロー2「システムエラーが発生しました。」を表示する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>清山</t>
     <rPh sb="0" eb="2">
       <t>セイヤマ</t>
@@ -384,10 +451,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>エラーメッセージ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>削除</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -459,96 +522,25 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>従業員(削除したいタスクの担当者本人)</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
+    <t>削除したタスクの内容が表示されている表</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移するボタン</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ホンニン</t>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
+    <t>メニュー画面へ遷移するボタン</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1:削除処理失敗
-E1-1:基本フロー7でシステムがタスク削除処理に失敗する
-E1-2:「システムエラーが発生しました。」を表示する
-E2:データベース接続失敗した場合
-E2-1:システムは削除失敗画面を表示する。
-E2-2:システムは「次のタスクを削除できませんでした」というエラーメッセージを表示する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>選択したタスクがデータベースで削除されタスク削除完了画面が表示される</t>
-    <rPh sb="0" eb="2">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1:タスク未選択で削除ボタン押下
-A1-1:基本フロー3でタスク未選択を検出
-A1-2:.タスク一覧表示画面で「タスクが存在しません」と表示される
-A1-3:従業員は基本フロー１に戻る</t>
-    <rPh sb="33" eb="36">
-      <t>ミセンタク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ケンシュツ</t>
-    </rPh>
-    <rPh sb="80" eb="83">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="91" eb="92">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.従業員がタスク一覧画面を表示する
-2.従業員が削除対象のタスクをラジオボタンで選択する
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する
-5.システムがタスク削除確認画面を表示する
-6.従業員が「削除」ボタンを押下する
-7.システムが選択されたタスクを削除する
-8.システムがタスク削除完了画面を表示する</t>
-    <rPh sb="2" eb="5">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="160" eb="166">
-      <t>サクジョカンリョウガメン</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>削除ができなかったタスクの内容が表示されている表</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1429,134 +1421,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1568,16 +1446,82 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1585,14 +1529,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1603,16 +1544,82 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1621,29 +1628,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1667,15 +1659,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>167566</xdr:rowOff>
+      <xdr:rowOff>148516</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1704,7 +1696,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="466725" y="1581150"/>
+          <a:off x="476250" y="1562100"/>
           <a:ext cx="3743325" cy="3444166"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1712,6 +1704,302 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>971550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="吹き出し: 線 (枠なし) 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74FBA6ED-C1D0-4CDA-9383-283B7414F59F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4229100" y="1952625"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 22199"/>
+            <a:gd name="adj2" fmla="val 5411"/>
+            <a:gd name="adj3" fmla="val 67672"/>
+            <a:gd name="adj4" fmla="val -12267"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="楕円 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2D310AE-6D1D-4302-A078-976719E40C60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="361950" y="4591050"/>
+          <a:ext cx="1552575" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>981075</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 線 (枠なし) 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECA8D36B-E823-4349-9CCB-73041ADF307B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3990975"/>
+          <a:ext cx="2009775" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 19900"/>
+            <a:gd name="adj2" fmla="val 11098"/>
+            <a:gd name="adj3" fmla="val 83764"/>
+            <a:gd name="adj4" fmla="val 28492"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B5C039-FA63-414F-8BF0-F06FCD268122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="409576" y="2505075"/>
+          <a:ext cx="3648074" cy="1971675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2220,23 +2508,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>295274</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:rowOff>19872</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>132589</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302AA3AC-8CDB-3AD0-3788-80E1EED4D995}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1BC69F2-883E-B64F-E640-D3D2BAF02075}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2258,8 +2546,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638174" y="1562099"/>
-          <a:ext cx="3866390" cy="3371851"/>
+          <a:off x="190501" y="1562922"/>
+          <a:ext cx="3771899" cy="3332928"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2271,15 +2559,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1085851</xdr:colOff>
+      <xdr:colOff>828676</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>238126</xdr:rowOff>
+      <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>590551</xdr:colOff>
+      <xdr:colOff>333376</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2294,7 +2582,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4343401" y="2047876"/>
+          <a:off x="4086226" y="2066926"/>
           <a:ext cx="1733550" cy="704850"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -2352,16 +2640,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2376,7 +2664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="4505325"/>
+          <a:off x="180975" y="4391025"/>
           <a:ext cx="1552575" cy="381000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -2418,82 +2706,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="楕円 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D7C6687-BA2B-4C76-9202-106029AAB8F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="790576" y="2190750"/>
-          <a:ext cx="2428874" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2508,7 +2730,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2705100" y="4552950"/>
+          <a:off x="2162175" y="4410075"/>
           <a:ext cx="2009775" cy="1362075"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -2566,98 +2788,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="吹き出し: 線 (枠なし) 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C662BBFC-F397-4483-830C-560C178F5EC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3514725" y="2152649"/>
-          <a:ext cx="1419225" cy="200025"/>
-        </a:xfrm>
-        <a:prstGeom prst="callout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 62757"/>
-            <a:gd name="adj2" fmla="val 7504"/>
-            <a:gd name="adj3" fmla="val 112500"/>
-            <a:gd name="adj4" fmla="val -29608"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" cap="none" spc="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t>③</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
+      <xdr:colOff>771525</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>219076</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2672,8 +2812,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="790575" y="2524126"/>
-          <a:ext cx="3409950" cy="1905000"/>
+          <a:off x="200024" y="2343151"/>
+          <a:ext cx="3829051" cy="2028824"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2922,85 +3062,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3020,46 +3160,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="71"/>
-      <c r="I13" s="79" t="s">
+      <c r="H13" s="40"/>
+      <c r="I13" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="71"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="79"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="71"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="79"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="71"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3068,13 +3208,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4088,19 +4228,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4112,192 +4252,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>46183</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="41" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="71"/>
-      <c r="D9" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="43"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="96" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="111" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="43"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="78"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5288,17 +5428,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5307,14 +5444,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5333,19 +5473,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5357,40 +5497,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="46"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6746,19 +6886,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6770,40 +6910,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="46"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8153,19 +8293,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8177,275 +8317,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>46188</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="46"/>
+      <c r="I2" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="59"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="59"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="59"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="59"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="59"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="59"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="59"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="97"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="59"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="97"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="59"/>
+      <c r="A16" s="71"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="60"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="59"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="59"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="59"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="97"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="43"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="71"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="71"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8458,103 +8598,119 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="72" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="A23" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+        <v>88</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="64"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
+      <c r="A24" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
+        <v>90</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="64"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="43"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="64"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="73"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="71"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="43"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="64"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="73"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="71"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="43"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="73"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="71"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="43"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="64"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="76"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="67"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="78"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="80"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9535,6 +9691,27 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A7:J19"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="H28:J28"/>
     <mergeCell ref="A29:C29"/>
@@ -9545,27 +9722,6 @@
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J19"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9588,19 +9744,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9612,287 +9768,287 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>46188</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="46"/>
+      <c r="I2" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="93" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="59"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="57"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="59"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="97"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="59"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="97"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="59"/>
+      <c r="A16" s="71"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="60"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="59"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="59"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="59"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="97"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="59"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="97"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="43"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="71"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="71"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -9905,131 +10061,131 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="72" t="s">
+      <c r="H23" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="64"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
+      <c r="A24" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="64"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="17" t="s">
-        <v>86</v>
-      </c>
       <c r="E25" s="17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="39"/>
+      <c r="J25" s="64"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="42"/>
-      <c r="J25" s="43"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="E26" s="17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="42"/>
-      <c r="J26" s="43"/>
+        <v>92</v>
+      </c>
+      <c r="H26" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="39"/>
+      <c r="J26" s="64"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="73"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="71"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="43"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="73"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="71"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="43"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="64"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="73"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="71"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="43"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="64"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="74"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="76"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="67"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="78"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="80"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11010,6 +11166,27 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J20"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="H29:J29"/>
     <mergeCell ref="A30:C30"/>
@@ -11020,27 +11197,6 @@
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J20"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11054,7 +11210,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1006"/>
+  <dimension ref="A1:J1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -11063,19 +11219,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11087,275 +11243,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>46188</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="46"/>
+      <c r="I2" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="59"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="59"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="59"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="59"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="97"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="59"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="97"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="59"/>
+      <c r="A16" s="71"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="60"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="59"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="59"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="59"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="97"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="43"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="71"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="71"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11368,108 +11524,109 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="72" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="A23" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+        <v>89</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="64"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
+      <c r="A24" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
+        <v>90</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="64"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38" t="s">
-        <v>75</v>
-      </c>
+      <c r="A25" s="85"/>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="17" t="s">
-        <v>85</v>
-      </c>
+      <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="43"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="64"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="73"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="71"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="43"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="64"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="73"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="71"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="43"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="73"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="43"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="78"/>
-    </row>
+      <c r="A28" s="86"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="80"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12446,18 +12603,20 @@
     <row r="1003" ht="12.75" customHeight="1"/>
     <row r="1004" ht="12.75" customHeight="1"/>
     <row r="1005" ht="12.75" customHeight="1"/>
-    <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+  <mergeCells count="29">
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="D5:J5"/>
@@ -12469,17 +12628,12 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
     <mergeCell ref="H28:J28"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12499,182 +12653,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="66" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="66" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="66" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="66" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="50"/>
-      <c r="S1" s="66" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="52"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="56"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="96"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="59"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="97"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="108"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="52"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="41" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="43"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="64"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="41" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="43"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="64"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12873,37 +13027,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="71"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="72" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="71"/>
-      <c r="G15" s="72" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="72" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="72" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="71"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -12915,37 +13069,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="105">
         <v>1</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="71"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="71"/>
-      <c r="G16" s="106" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="106" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="71"/>
-      <c r="L16" s="104" t="s">
+      <c r="K16" s="40"/>
+      <c r="L16" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="104" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="71"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12957,37 +13111,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="105">
         <v>2</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="101" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="71"/>
-      <c r="G17" s="106" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="71"/>
-      <c r="L17" s="104" t="s">
+      <c r="K17" s="40"/>
+      <c r="L17" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="104" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="71"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12999,23 +13153,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="71"/>
+      <c r="A18" s="105"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13027,23 +13181,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="71"/>
+      <c r="A19" s="105"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13055,23 +13209,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="71"/>
+      <c r="A20" s="105"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13083,23 +13237,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="104"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="71"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13111,23 +13265,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="71"/>
+      <c r="A22" s="105"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13139,23 +13293,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="71"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13167,23 +13321,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="71"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13195,23 +13349,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="71"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13223,23 +13377,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="71"/>
+      <c r="A26" s="105"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13251,23 +13405,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="71"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13279,23 +13433,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="71"/>
+      <c r="A28" s="105"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13307,23 +13461,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="104"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="71"/>
+      <c r="A29" s="105"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13335,23 +13489,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="71"/>
+      <c r="A30" s="105"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13363,23 +13517,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="76"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="67"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14377,62 +14531,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14457,62 +14611,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
